--- a/envio_periodicos_app/xlsx_templates/MODELO_BASE_DIRECIONADA.xlsx
+++ b/envio_periodicos_app/xlsx_templates/MODELO_BASE_DIRECIONADA.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BASE DIRECIONADA" sheetId="1" r:id="R86397cb40e634941"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BASE DIRECIONADA" sheetId="1" r:id="R5351c16a31c44521"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -34,7 +34,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF163A5F"/>
+        <x:fgColor rgb="FF153E5C"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -45,7 +45,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="11">
+  <x:cellXfs count="12">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -63,6 +63,9 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
@@ -269,813 +272,821 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="42" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="42" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="30" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="32" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="5" t="str">
-        <x:v>EMPRESA</x:v>
+      <x:c r="A1" s="10" t="str">
+        <x:v>EMPRESA / CNPJ</x:v>
       </x:c>
-      <x:c r="B1" s="5" t="str">
+      <x:c r="B1" s="10" t="str">
         <x:v>NOME DO FUNCIONÁRIO</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="10"/>
-      <x:c r="B2" s="10"/>
+      <x:c r="A2" s="11" t="str">
+        <x:v>12.345.678/0001-90</x:v>
+      </x:c>
+      <x:c r="B2" s="11" t="str">
+        <x:v>JOÃO DA SILVA</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="10"/>
-      <x:c r="B3" s="10"/>
+      <x:c r="A3" s="11" t="str">
+        <x:v>EMPRESA EXEMPLO LTDA</x:v>
+      </x:c>
+      <x:c r="B3" s="11" t="str">
+        <x:v>MARIA DE SOUZA</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="10"/>
-      <x:c r="B4" s="10"/>
+      <x:c r="A4" s="11" t="str"/>
+      <x:c r="B4" s="11" t="str"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="10"/>
-      <x:c r="B5" s="10"/>
+      <x:c r="A5" s="11"/>
+      <x:c r="B5" s="11"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="10"/>
-      <x:c r="B6" s="10"/>
+      <x:c r="A6" s="11"/>
+      <x:c r="B6" s="11"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="10"/>
-      <x:c r="B7" s="10"/>
+      <x:c r="A7" s="11"/>
+      <x:c r="B7" s="11"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="10"/>
-      <x:c r="B8" s="10"/>
+      <x:c r="A8" s="11"/>
+      <x:c r="B8" s="11"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="10"/>
-      <x:c r="B9" s="10"/>
+      <x:c r="A9" s="11"/>
+      <x:c r="B9" s="11"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="10"/>
-      <x:c r="B10" s="10"/>
+      <x:c r="A10" s="11"/>
+      <x:c r="B10" s="11"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="10"/>
-      <x:c r="B11" s="10"/>
+      <x:c r="A11" s="11"/>
+      <x:c r="B11" s="11"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="10"/>
-      <x:c r="B12" s="10"/>
+      <x:c r="A12" s="11"/>
+      <x:c r="B12" s="11"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="10"/>
-      <x:c r="B13" s="10"/>
+      <x:c r="A13" s="11"/>
+      <x:c r="B13" s="11"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="10"/>
-      <x:c r="B14" s="10"/>
+      <x:c r="A14" s="11"/>
+      <x:c r="B14" s="11"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="10"/>
-      <x:c r="B15" s="10"/>
+      <x:c r="A15" s="11"/>
+      <x:c r="B15" s="11"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="10"/>
-      <x:c r="B16" s="10"/>
+      <x:c r="A16" s="11"/>
+      <x:c r="B16" s="11"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="10"/>
-      <x:c r="B17" s="10"/>
+      <x:c r="A17" s="11"/>
+      <x:c r="B17" s="11"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="10"/>
-      <x:c r="B18" s="10"/>
+      <x:c r="A18" s="11"/>
+      <x:c r="B18" s="11"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="10"/>
-      <x:c r="B19" s="10"/>
+      <x:c r="A19" s="11"/>
+      <x:c r="B19" s="11"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="10"/>
-      <x:c r="B20" s="10"/>
+      <x:c r="A20" s="11"/>
+      <x:c r="B20" s="11"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="10"/>
-      <x:c r="B21" s="10"/>
+      <x:c r="A21" s="11"/>
+      <x:c r="B21" s="11"/>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="10"/>
-      <x:c r="B22" s="10"/>
+      <x:c r="A22" s="11"/>
+      <x:c r="B22" s="11"/>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="10"/>
-      <x:c r="B23" s="10"/>
+      <x:c r="A23" s="11"/>
+      <x:c r="B23" s="11"/>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="10"/>
-      <x:c r="B24" s="10"/>
+      <x:c r="A24" s="11"/>
+      <x:c r="B24" s="11"/>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="10"/>
-      <x:c r="B25" s="10"/>
+      <x:c r="A25" s="11"/>
+      <x:c r="B25" s="11"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="10"/>
-      <x:c r="B26" s="10"/>
+      <x:c r="A26" s="11"/>
+      <x:c r="B26" s="11"/>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="10"/>
-      <x:c r="B27" s="10"/>
+      <x:c r="A27" s="11"/>
+      <x:c r="B27" s="11"/>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="10"/>
-      <x:c r="B28" s="10"/>
+      <x:c r="A28" s="11"/>
+      <x:c r="B28" s="11"/>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" s="10"/>
-      <x:c r="B29" s="10"/>
+      <x:c r="A29" s="11"/>
+      <x:c r="B29" s="11"/>
     </x:row>
     <x:row r="30">
-      <x:c r="A30" s="10"/>
-      <x:c r="B30" s="10"/>
+      <x:c r="A30" s="11"/>
+      <x:c r="B30" s="11"/>
     </x:row>
     <x:row r="31">
-      <x:c r="A31" s="10"/>
-      <x:c r="B31" s="10"/>
+      <x:c r="A31" s="11"/>
+      <x:c r="B31" s="11"/>
     </x:row>
     <x:row r="32">
-      <x:c r="A32" s="10"/>
-      <x:c r="B32" s="10"/>
+      <x:c r="A32" s="11"/>
+      <x:c r="B32" s="11"/>
     </x:row>
     <x:row r="33">
-      <x:c r="A33" s="10"/>
-      <x:c r="B33" s="10"/>
+      <x:c r="A33" s="11"/>
+      <x:c r="B33" s="11"/>
     </x:row>
     <x:row r="34">
-      <x:c r="A34" s="10"/>
-      <x:c r="B34" s="10"/>
+      <x:c r="A34" s="11"/>
+      <x:c r="B34" s="11"/>
     </x:row>
     <x:row r="35">
-      <x:c r="A35" s="10"/>
-      <x:c r="B35" s="10"/>
+      <x:c r="A35" s="11"/>
+      <x:c r="B35" s="11"/>
     </x:row>
     <x:row r="36">
-      <x:c r="A36" s="10"/>
-      <x:c r="B36" s="10"/>
+      <x:c r="A36" s="11"/>
+      <x:c r="B36" s="11"/>
     </x:row>
     <x:row r="37">
-      <x:c r="A37" s="10"/>
-      <x:c r="B37" s="10"/>
+      <x:c r="A37" s="11"/>
+      <x:c r="B37" s="11"/>
     </x:row>
     <x:row r="38">
-      <x:c r="A38" s="10"/>
-      <x:c r="B38" s="10"/>
+      <x:c r="A38" s="11"/>
+      <x:c r="B38" s="11"/>
     </x:row>
     <x:row r="39">
-      <x:c r="A39" s="10"/>
-      <x:c r="B39" s="10"/>
+      <x:c r="A39" s="11"/>
+      <x:c r="B39" s="11"/>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" s="10"/>
-      <x:c r="B40" s="10"/>
+      <x:c r="A40" s="11"/>
+      <x:c r="B40" s="11"/>
     </x:row>
     <x:row r="41">
-      <x:c r="A41" s="10"/>
-      <x:c r="B41" s="10"/>
+      <x:c r="A41" s="11"/>
+      <x:c r="B41" s="11"/>
     </x:row>
     <x:row r="42">
-      <x:c r="A42" s="10"/>
-      <x:c r="B42" s="10"/>
+      <x:c r="A42" s="11"/>
+      <x:c r="B42" s="11"/>
     </x:row>
     <x:row r="43">
-      <x:c r="A43" s="10"/>
-      <x:c r="B43" s="10"/>
+      <x:c r="A43" s="11"/>
+      <x:c r="B43" s="11"/>
     </x:row>
     <x:row r="44">
-      <x:c r="A44" s="10"/>
-      <x:c r="B44" s="10"/>
+      <x:c r="A44" s="11"/>
+      <x:c r="B44" s="11"/>
     </x:row>
     <x:row r="45">
-      <x:c r="A45" s="10"/>
-      <x:c r="B45" s="10"/>
+      <x:c r="A45" s="11"/>
+      <x:c r="B45" s="11"/>
     </x:row>
     <x:row r="46">
-      <x:c r="A46" s="10"/>
-      <x:c r="B46" s="10"/>
+      <x:c r="A46" s="11"/>
+      <x:c r="B46" s="11"/>
     </x:row>
     <x:row r="47">
-      <x:c r="A47" s="10"/>
-      <x:c r="B47" s="10"/>
+      <x:c r="A47" s="11"/>
+      <x:c r="B47" s="11"/>
     </x:row>
     <x:row r="48">
-      <x:c r="A48" s="10"/>
-      <x:c r="B48" s="10"/>
+      <x:c r="A48" s="11"/>
+      <x:c r="B48" s="11"/>
     </x:row>
     <x:row r="49">
-      <x:c r="A49" s="10"/>
-      <x:c r="B49" s="10"/>
+      <x:c r="A49" s="11"/>
+      <x:c r="B49" s="11"/>
     </x:row>
     <x:row r="50">
-      <x:c r="A50" s="10"/>
-      <x:c r="B50" s="10"/>
+      <x:c r="A50" s="11"/>
+      <x:c r="B50" s="11"/>
     </x:row>
     <x:row r="51">
-      <x:c r="A51" s="10"/>
-      <x:c r="B51" s="10"/>
+      <x:c r="A51" s="11"/>
+      <x:c r="B51" s="11"/>
     </x:row>
     <x:row r="52">
-      <x:c r="A52" s="10"/>
-      <x:c r="B52" s="10"/>
+      <x:c r="A52" s="11"/>
+      <x:c r="B52" s="11"/>
     </x:row>
     <x:row r="53">
-      <x:c r="A53" s="10"/>
-      <x:c r="B53" s="10"/>
+      <x:c r="A53" s="11"/>
+      <x:c r="B53" s="11"/>
     </x:row>
     <x:row r="54">
-      <x:c r="A54" s="10"/>
-      <x:c r="B54" s="10"/>
+      <x:c r="A54" s="11"/>
+      <x:c r="B54" s="11"/>
     </x:row>
     <x:row r="55">
-      <x:c r="A55" s="10"/>
-      <x:c r="B55" s="10"/>
+      <x:c r="A55" s="11"/>
+      <x:c r="B55" s="11"/>
     </x:row>
     <x:row r="56">
-      <x:c r="A56" s="10"/>
-      <x:c r="B56" s="10"/>
+      <x:c r="A56" s="11"/>
+      <x:c r="B56" s="11"/>
     </x:row>
     <x:row r="57">
-      <x:c r="A57" s="10"/>
-      <x:c r="B57" s="10"/>
+      <x:c r="A57" s="11"/>
+      <x:c r="B57" s="11"/>
     </x:row>
     <x:row r="58">
-      <x:c r="A58" s="10"/>
-      <x:c r="B58" s="10"/>
+      <x:c r="A58" s="11"/>
+      <x:c r="B58" s="11"/>
     </x:row>
     <x:row r="59">
-      <x:c r="A59" s="10"/>
-      <x:c r="B59" s="10"/>
+      <x:c r="A59" s="11"/>
+      <x:c r="B59" s="11"/>
     </x:row>
     <x:row r="60">
-      <x:c r="A60" s="10"/>
-      <x:c r="B60" s="10"/>
+      <x:c r="A60" s="11"/>
+      <x:c r="B60" s="11"/>
     </x:row>
     <x:row r="61">
-      <x:c r="A61" s="10"/>
-      <x:c r="B61" s="10"/>
+      <x:c r="A61" s="11"/>
+      <x:c r="B61" s="11"/>
     </x:row>
     <x:row r="62">
-      <x:c r="A62" s="10"/>
-      <x:c r="B62" s="10"/>
+      <x:c r="A62" s="11"/>
+      <x:c r="B62" s="11"/>
     </x:row>
     <x:row r="63">
-      <x:c r="A63" s="10"/>
-      <x:c r="B63" s="10"/>
+      <x:c r="A63" s="11"/>
+      <x:c r="B63" s="11"/>
     </x:row>
     <x:row r="64">
-      <x:c r="A64" s="10"/>
-      <x:c r="B64" s="10"/>
+      <x:c r="A64" s="11"/>
+      <x:c r="B64" s="11"/>
     </x:row>
     <x:row r="65">
-      <x:c r="A65" s="10"/>
-      <x:c r="B65" s="10"/>
+      <x:c r="A65" s="11"/>
+      <x:c r="B65" s="11"/>
     </x:row>
     <x:row r="66">
-      <x:c r="A66" s="10"/>
-      <x:c r="B66" s="10"/>
+      <x:c r="A66" s="11"/>
+      <x:c r="B66" s="11"/>
     </x:row>
     <x:row r="67">
-      <x:c r="A67" s="10"/>
-      <x:c r="B67" s="10"/>
+      <x:c r="A67" s="11"/>
+      <x:c r="B67" s="11"/>
     </x:row>
     <x:row r="68">
-      <x:c r="A68" s="10"/>
-      <x:c r="B68" s="10"/>
+      <x:c r="A68" s="11"/>
+      <x:c r="B68" s="11"/>
     </x:row>
     <x:row r="69">
-      <x:c r="A69" s="10"/>
-      <x:c r="B69" s="10"/>
+      <x:c r="A69" s="11"/>
+      <x:c r="B69" s="11"/>
     </x:row>
     <x:row r="70">
-      <x:c r="A70" s="10"/>
-      <x:c r="B70" s="10"/>
+      <x:c r="A70" s="11"/>
+      <x:c r="B70" s="11"/>
     </x:row>
     <x:row r="71">
-      <x:c r="A71" s="10"/>
-      <x:c r="B71" s="10"/>
+      <x:c r="A71" s="11"/>
+      <x:c r="B71" s="11"/>
     </x:row>
     <x:row r="72">
-      <x:c r="A72" s="10"/>
-      <x:c r="B72" s="10"/>
+      <x:c r="A72" s="11"/>
+      <x:c r="B72" s="11"/>
     </x:row>
     <x:row r="73">
-      <x:c r="A73" s="10"/>
-      <x:c r="B73" s="10"/>
+      <x:c r="A73" s="11"/>
+      <x:c r="B73" s="11"/>
     </x:row>
     <x:row r="74">
-      <x:c r="A74" s="10"/>
-      <x:c r="B74" s="10"/>
+      <x:c r="A74" s="11"/>
+      <x:c r="B74" s="11"/>
     </x:row>
     <x:row r="75">
-      <x:c r="A75" s="10"/>
-      <x:c r="B75" s="10"/>
+      <x:c r="A75" s="11"/>
+      <x:c r="B75" s="11"/>
     </x:row>
     <x:row r="76">
-      <x:c r="A76" s="10"/>
-      <x:c r="B76" s="10"/>
+      <x:c r="A76" s="11"/>
+      <x:c r="B76" s="11"/>
     </x:row>
     <x:row r="77">
-      <x:c r="A77" s="10"/>
-      <x:c r="B77" s="10"/>
+      <x:c r="A77" s="11"/>
+      <x:c r="B77" s="11"/>
     </x:row>
     <x:row r="78">
-      <x:c r="A78" s="10"/>
-      <x:c r="B78" s="10"/>
+      <x:c r="A78" s="11"/>
+      <x:c r="B78" s="11"/>
     </x:row>
     <x:row r="79">
-      <x:c r="A79" s="10"/>
-      <x:c r="B79" s="10"/>
+      <x:c r="A79" s="11"/>
+      <x:c r="B79" s="11"/>
     </x:row>
     <x:row r="80">
-      <x:c r="A80" s="10"/>
-      <x:c r="B80" s="10"/>
+      <x:c r="A80" s="11"/>
+      <x:c r="B80" s="11"/>
     </x:row>
     <x:row r="81">
-      <x:c r="A81" s="10"/>
-      <x:c r="B81" s="10"/>
+      <x:c r="A81" s="11"/>
+      <x:c r="B81" s="11"/>
     </x:row>
     <x:row r="82">
-      <x:c r="A82" s="10"/>
-      <x:c r="B82" s="10"/>
+      <x:c r="A82" s="11"/>
+      <x:c r="B82" s="11"/>
     </x:row>
     <x:row r="83">
-      <x:c r="A83" s="10"/>
-      <x:c r="B83" s="10"/>
+      <x:c r="A83" s="11"/>
+      <x:c r="B83" s="11"/>
     </x:row>
     <x:row r="84">
-      <x:c r="A84" s="10"/>
-      <x:c r="B84" s="10"/>
+      <x:c r="A84" s="11"/>
+      <x:c r="B84" s="11"/>
     </x:row>
     <x:row r="85">
-      <x:c r="A85" s="10"/>
-      <x:c r="B85" s="10"/>
+      <x:c r="A85" s="11"/>
+      <x:c r="B85" s="11"/>
     </x:row>
     <x:row r="86">
-      <x:c r="A86" s="10"/>
-      <x:c r="B86" s="10"/>
+      <x:c r="A86" s="11"/>
+      <x:c r="B86" s="11"/>
     </x:row>
     <x:row r="87">
-      <x:c r="A87" s="10"/>
-      <x:c r="B87" s="10"/>
+      <x:c r="A87" s="11"/>
+      <x:c r="B87" s="11"/>
     </x:row>
     <x:row r="88">
-      <x:c r="A88" s="10"/>
-      <x:c r="B88" s="10"/>
+      <x:c r="A88" s="11"/>
+      <x:c r="B88" s="11"/>
     </x:row>
     <x:row r="89">
-      <x:c r="A89" s="10"/>
-      <x:c r="B89" s="10"/>
+      <x:c r="A89" s="11"/>
+      <x:c r="B89" s="11"/>
     </x:row>
     <x:row r="90">
-      <x:c r="A90" s="10"/>
-      <x:c r="B90" s="10"/>
+      <x:c r="A90" s="11"/>
+      <x:c r="B90" s="11"/>
     </x:row>
     <x:row r="91">
-      <x:c r="A91" s="10"/>
-      <x:c r="B91" s="10"/>
+      <x:c r="A91" s="11"/>
+      <x:c r="B91" s="11"/>
     </x:row>
     <x:row r="92">
-      <x:c r="A92" s="10"/>
-      <x:c r="B92" s="10"/>
+      <x:c r="A92" s="11"/>
+      <x:c r="B92" s="11"/>
     </x:row>
     <x:row r="93">
-      <x:c r="A93" s="10"/>
-      <x:c r="B93" s="10"/>
+      <x:c r="A93" s="11"/>
+      <x:c r="B93" s="11"/>
     </x:row>
     <x:row r="94">
-      <x:c r="A94" s="10"/>
-      <x:c r="B94" s="10"/>
+      <x:c r="A94" s="11"/>
+      <x:c r="B94" s="11"/>
     </x:row>
     <x:row r="95">
-      <x:c r="A95" s="10"/>
-      <x:c r="B95" s="10"/>
+      <x:c r="A95" s="11"/>
+      <x:c r="B95" s="11"/>
     </x:row>
     <x:row r="96">
-      <x:c r="A96" s="10"/>
-      <x:c r="B96" s="10"/>
+      <x:c r="A96" s="11"/>
+      <x:c r="B96" s="11"/>
     </x:row>
     <x:row r="97">
-      <x:c r="A97" s="10"/>
-      <x:c r="B97" s="10"/>
+      <x:c r="A97" s="11"/>
+      <x:c r="B97" s="11"/>
     </x:row>
     <x:row r="98">
-      <x:c r="A98" s="10"/>
-      <x:c r="B98" s="10"/>
+      <x:c r="A98" s="11"/>
+      <x:c r="B98" s="11"/>
     </x:row>
     <x:row r="99">
-      <x:c r="A99" s="10"/>
-      <x:c r="B99" s="10"/>
+      <x:c r="A99" s="11"/>
+      <x:c r="B99" s="11"/>
     </x:row>
     <x:row r="100">
-      <x:c r="A100" s="10"/>
-      <x:c r="B100" s="10"/>
+      <x:c r="A100" s="11"/>
+      <x:c r="B100" s="11"/>
     </x:row>
     <x:row r="101">
-      <x:c r="A101" s="10"/>
-      <x:c r="B101" s="10"/>
+      <x:c r="A101" s="11"/>
+      <x:c r="B101" s="11"/>
     </x:row>
     <x:row r="102">
-      <x:c r="A102" s="10"/>
-      <x:c r="B102" s="10"/>
+      <x:c r="A102" s="11"/>
+      <x:c r="B102" s="11"/>
     </x:row>
     <x:row r="103">
-      <x:c r="A103" s="10"/>
-      <x:c r="B103" s="10"/>
+      <x:c r="A103" s="11"/>
+      <x:c r="B103" s="11"/>
     </x:row>
     <x:row r="104">
-      <x:c r="A104" s="10"/>
-      <x:c r="B104" s="10"/>
+      <x:c r="A104" s="11"/>
+      <x:c r="B104" s="11"/>
     </x:row>
     <x:row r="105">
-      <x:c r="A105" s="10"/>
-      <x:c r="B105" s="10"/>
+      <x:c r="A105" s="11"/>
+      <x:c r="B105" s="11"/>
     </x:row>
     <x:row r="106">
-      <x:c r="A106" s="10"/>
-      <x:c r="B106" s="10"/>
+      <x:c r="A106" s="11"/>
+      <x:c r="B106" s="11"/>
     </x:row>
     <x:row r="107">
-      <x:c r="A107" s="10"/>
-      <x:c r="B107" s="10"/>
+      <x:c r="A107" s="11"/>
+      <x:c r="B107" s="11"/>
     </x:row>
     <x:row r="108">
-      <x:c r="A108" s="10"/>
-      <x:c r="B108" s="10"/>
+      <x:c r="A108" s="11"/>
+      <x:c r="B108" s="11"/>
     </x:row>
     <x:row r="109">
-      <x:c r="A109" s="10"/>
-      <x:c r="B109" s="10"/>
+      <x:c r="A109" s="11"/>
+      <x:c r="B109" s="11"/>
     </x:row>
     <x:row r="110">
-      <x:c r="A110" s="10"/>
-      <x:c r="B110" s="10"/>
+      <x:c r="A110" s="11"/>
+      <x:c r="B110" s="11"/>
     </x:row>
     <x:row r="111">
-      <x:c r="A111" s="10"/>
-      <x:c r="B111" s="10"/>
+      <x:c r="A111" s="11"/>
+      <x:c r="B111" s="11"/>
     </x:row>
     <x:row r="112">
-      <x:c r="A112" s="10"/>
-      <x:c r="B112" s="10"/>
+      <x:c r="A112" s="11"/>
+      <x:c r="B112" s="11"/>
     </x:row>
     <x:row r="113">
-      <x:c r="A113" s="10"/>
-      <x:c r="B113" s="10"/>
+      <x:c r="A113" s="11"/>
+      <x:c r="B113" s="11"/>
     </x:row>
     <x:row r="114">
-      <x:c r="A114" s="10"/>
-      <x:c r="B114" s="10"/>
+      <x:c r="A114" s="11"/>
+      <x:c r="B114" s="11"/>
     </x:row>
     <x:row r="115">
-      <x:c r="A115" s="10"/>
-      <x:c r="B115" s="10"/>
+      <x:c r="A115" s="11"/>
+      <x:c r="B115" s="11"/>
     </x:row>
     <x:row r="116">
-      <x:c r="A116" s="10"/>
-      <x:c r="B116" s="10"/>
+      <x:c r="A116" s="11"/>
+      <x:c r="B116" s="11"/>
     </x:row>
     <x:row r="117">
-      <x:c r="A117" s="10"/>
-      <x:c r="B117" s="10"/>
+      <x:c r="A117" s="11"/>
+      <x:c r="B117" s="11"/>
     </x:row>
     <x:row r="118">
-      <x:c r="A118" s="10"/>
-      <x:c r="B118" s="10"/>
+      <x:c r="A118" s="11"/>
+      <x:c r="B118" s="11"/>
     </x:row>
     <x:row r="119">
-      <x:c r="A119" s="10"/>
-      <x:c r="B119" s="10"/>
+      <x:c r="A119" s="11"/>
+      <x:c r="B119" s="11"/>
     </x:row>
     <x:row r="120">
-      <x:c r="A120" s="10"/>
-      <x:c r="B120" s="10"/>
+      <x:c r="A120" s="11"/>
+      <x:c r="B120" s="11"/>
     </x:row>
     <x:row r="121">
-      <x:c r="A121" s="10"/>
-      <x:c r="B121" s="10"/>
+      <x:c r="A121" s="11"/>
+      <x:c r="B121" s="11"/>
     </x:row>
     <x:row r="122">
-      <x:c r="A122" s="10"/>
-      <x:c r="B122" s="10"/>
+      <x:c r="A122" s="11"/>
+      <x:c r="B122" s="11"/>
     </x:row>
     <x:row r="123">
-      <x:c r="A123" s="10"/>
-      <x:c r="B123" s="10"/>
+      <x:c r="A123" s="11"/>
+      <x:c r="B123" s="11"/>
     </x:row>
     <x:row r="124">
-      <x:c r="A124" s="10"/>
-      <x:c r="B124" s="10"/>
+      <x:c r="A124" s="11"/>
+      <x:c r="B124" s="11"/>
     </x:row>
     <x:row r="125">
-      <x:c r="A125" s="10"/>
-      <x:c r="B125" s="10"/>
+      <x:c r="A125" s="11"/>
+      <x:c r="B125" s="11"/>
     </x:row>
     <x:row r="126">
-      <x:c r="A126" s="10"/>
-      <x:c r="B126" s="10"/>
+      <x:c r="A126" s="11"/>
+      <x:c r="B126" s="11"/>
     </x:row>
     <x:row r="127">
-      <x:c r="A127" s="10"/>
-      <x:c r="B127" s="10"/>
+      <x:c r="A127" s="11"/>
+      <x:c r="B127" s="11"/>
     </x:row>
     <x:row r="128">
-      <x:c r="A128" s="10"/>
-      <x:c r="B128" s="10"/>
+      <x:c r="A128" s="11"/>
+      <x:c r="B128" s="11"/>
     </x:row>
     <x:row r="129">
-      <x:c r="A129" s="10"/>
-      <x:c r="B129" s="10"/>
+      <x:c r="A129" s="11"/>
+      <x:c r="B129" s="11"/>
     </x:row>
     <x:row r="130">
-      <x:c r="A130" s="10"/>
-      <x:c r="B130" s="10"/>
+      <x:c r="A130" s="11"/>
+      <x:c r="B130" s="11"/>
     </x:row>
     <x:row r="131">
-      <x:c r="A131" s="10"/>
-      <x:c r="B131" s="10"/>
+      <x:c r="A131" s="11"/>
+      <x:c r="B131" s="11"/>
     </x:row>
     <x:row r="132">
-      <x:c r="A132" s="10"/>
-      <x:c r="B132" s="10"/>
+      <x:c r="A132" s="11"/>
+      <x:c r="B132" s="11"/>
     </x:row>
     <x:row r="133">
-      <x:c r="A133" s="10"/>
-      <x:c r="B133" s="10"/>
+      <x:c r="A133" s="11"/>
+      <x:c r="B133" s="11"/>
     </x:row>
     <x:row r="134">
-      <x:c r="A134" s="10"/>
-      <x:c r="B134" s="10"/>
+      <x:c r="A134" s="11"/>
+      <x:c r="B134" s="11"/>
     </x:row>
     <x:row r="135">
-      <x:c r="A135" s="10"/>
-      <x:c r="B135" s="10"/>
+      <x:c r="A135" s="11"/>
+      <x:c r="B135" s="11"/>
     </x:row>
     <x:row r="136">
-      <x:c r="A136" s="10"/>
-      <x:c r="B136" s="10"/>
+      <x:c r="A136" s="11"/>
+      <x:c r="B136" s="11"/>
     </x:row>
     <x:row r="137">
-      <x:c r="A137" s="10"/>
-      <x:c r="B137" s="10"/>
+      <x:c r="A137" s="11"/>
+      <x:c r="B137" s="11"/>
     </x:row>
     <x:row r="138">
-      <x:c r="A138" s="10"/>
-      <x:c r="B138" s="10"/>
+      <x:c r="A138" s="11"/>
+      <x:c r="B138" s="11"/>
     </x:row>
     <x:row r="139">
-      <x:c r="A139" s="10"/>
-      <x:c r="B139" s="10"/>
+      <x:c r="A139" s="11"/>
+      <x:c r="B139" s="11"/>
     </x:row>
     <x:row r="140">
-      <x:c r="A140" s="10"/>
-      <x:c r="B140" s="10"/>
+      <x:c r="A140" s="11"/>
+      <x:c r="B140" s="11"/>
     </x:row>
     <x:row r="141">
-      <x:c r="A141" s="10"/>
-      <x:c r="B141" s="10"/>
+      <x:c r="A141" s="11"/>
+      <x:c r="B141" s="11"/>
     </x:row>
     <x:row r="142">
-      <x:c r="A142" s="10"/>
-      <x:c r="B142" s="10"/>
+      <x:c r="A142" s="11"/>
+      <x:c r="B142" s="11"/>
     </x:row>
     <x:row r="143">
-      <x:c r="A143" s="10"/>
-      <x:c r="B143" s="10"/>
+      <x:c r="A143" s="11"/>
+      <x:c r="B143" s="11"/>
     </x:row>
     <x:row r="144">
-      <x:c r="A144" s="10"/>
-      <x:c r="B144" s="10"/>
+      <x:c r="A144" s="11"/>
+      <x:c r="B144" s="11"/>
     </x:row>
     <x:row r="145">
-      <x:c r="A145" s="10"/>
-      <x:c r="B145" s="10"/>
+      <x:c r="A145" s="11"/>
+      <x:c r="B145" s="11"/>
     </x:row>
     <x:row r="146">
-      <x:c r="A146" s="10"/>
-      <x:c r="B146" s="10"/>
+      <x:c r="A146" s="11"/>
+      <x:c r="B146" s="11"/>
     </x:row>
     <x:row r="147">
-      <x:c r="A147" s="10"/>
-      <x:c r="B147" s="10"/>
+      <x:c r="A147" s="11"/>
+      <x:c r="B147" s="11"/>
     </x:row>
     <x:row r="148">
-      <x:c r="A148" s="10"/>
-      <x:c r="B148" s="10"/>
+      <x:c r="A148" s="11"/>
+      <x:c r="B148" s="11"/>
     </x:row>
     <x:row r="149">
-      <x:c r="A149" s="10"/>
-      <x:c r="B149" s="10"/>
+      <x:c r="A149" s="11"/>
+      <x:c r="B149" s="11"/>
     </x:row>
     <x:row r="150">
-      <x:c r="A150" s="10"/>
-      <x:c r="B150" s="10"/>
+      <x:c r="A150" s="11"/>
+      <x:c r="B150" s="11"/>
     </x:row>
     <x:row r="151">
-      <x:c r="A151" s="10"/>
-      <x:c r="B151" s="10"/>
+      <x:c r="A151" s="11"/>
+      <x:c r="B151" s="11"/>
     </x:row>
     <x:row r="152">
-      <x:c r="A152" s="10"/>
-      <x:c r="B152" s="10"/>
+      <x:c r="A152" s="11"/>
+      <x:c r="B152" s="11"/>
     </x:row>
     <x:row r="153">
-      <x:c r="A153" s="10"/>
-      <x:c r="B153" s="10"/>
+      <x:c r="A153" s="11"/>
+      <x:c r="B153" s="11"/>
     </x:row>
     <x:row r="154">
-      <x:c r="A154" s="10"/>
-      <x:c r="B154" s="10"/>
+      <x:c r="A154" s="11"/>
+      <x:c r="B154" s="11"/>
     </x:row>
     <x:row r="155">
-      <x:c r="A155" s="10"/>
-      <x:c r="B155" s="10"/>
+      <x:c r="A155" s="11"/>
+      <x:c r="B155" s="11"/>
     </x:row>
     <x:row r="156">
-      <x:c r="A156" s="10"/>
-      <x:c r="B156" s="10"/>
+      <x:c r="A156" s="11"/>
+      <x:c r="B156" s="11"/>
     </x:row>
     <x:row r="157">
-      <x:c r="A157" s="10"/>
-      <x:c r="B157" s="10"/>
+      <x:c r="A157" s="11"/>
+      <x:c r="B157" s="11"/>
     </x:row>
     <x:row r="158">
-      <x:c r="A158" s="10"/>
-      <x:c r="B158" s="10"/>
+      <x:c r="A158" s="11"/>
+      <x:c r="B158" s="11"/>
     </x:row>
     <x:row r="159">
-      <x:c r="A159" s="10"/>
-      <x:c r="B159" s="10"/>
+      <x:c r="A159" s="11"/>
+      <x:c r="B159" s="11"/>
     </x:row>
     <x:row r="160">
-      <x:c r="A160" s="10"/>
-      <x:c r="B160" s="10"/>
+      <x:c r="A160" s="11"/>
+      <x:c r="B160" s="11"/>
     </x:row>
     <x:row r="161">
-      <x:c r="A161" s="10"/>
-      <x:c r="B161" s="10"/>
+      <x:c r="A161" s="11"/>
+      <x:c r="B161" s="11"/>
     </x:row>
     <x:row r="162">
-      <x:c r="A162" s="10"/>
-      <x:c r="B162" s="10"/>
+      <x:c r="A162" s="11"/>
+      <x:c r="B162" s="11"/>
     </x:row>
     <x:row r="163">
-      <x:c r="A163" s="10"/>
-      <x:c r="B163" s="10"/>
+      <x:c r="A163" s="11"/>
+      <x:c r="B163" s="11"/>
     </x:row>
     <x:row r="164">
-      <x:c r="A164" s="10"/>
-      <x:c r="B164" s="10"/>
+      <x:c r="A164" s="11"/>
+      <x:c r="B164" s="11"/>
     </x:row>
     <x:row r="165">
-      <x:c r="A165" s="10"/>
-      <x:c r="B165" s="10"/>
+      <x:c r="A165" s="11"/>
+      <x:c r="B165" s="11"/>
     </x:row>
     <x:row r="166">
-      <x:c r="A166" s="10"/>
-      <x:c r="B166" s="10"/>
+      <x:c r="A166" s="11"/>
+      <x:c r="B166" s="11"/>
     </x:row>
     <x:row r="167">
-      <x:c r="A167" s="10"/>
-      <x:c r="B167" s="10"/>
+      <x:c r="A167" s="11"/>
+      <x:c r="B167" s="11"/>
     </x:row>
     <x:row r="168">
-      <x:c r="A168" s="10"/>
-      <x:c r="B168" s="10"/>
+      <x:c r="A168" s="11"/>
+      <x:c r="B168" s="11"/>
     </x:row>
     <x:row r="169">
-      <x:c r="A169" s="10"/>
-      <x:c r="B169" s="10"/>
+      <x:c r="A169" s="11"/>
+      <x:c r="B169" s="11"/>
     </x:row>
     <x:row r="170">
-      <x:c r="A170" s="10"/>
-      <x:c r="B170" s="10"/>
+      <x:c r="A170" s="11"/>
+      <x:c r="B170" s="11"/>
     </x:row>
     <x:row r="171">
-      <x:c r="A171" s="10"/>
-      <x:c r="B171" s="10"/>
+      <x:c r="A171" s="11"/>
+      <x:c r="B171" s="11"/>
     </x:row>
     <x:row r="172">
-      <x:c r="A172" s="10"/>
-      <x:c r="B172" s="10"/>
+      <x:c r="A172" s="11"/>
+      <x:c r="B172" s="11"/>
     </x:row>
     <x:row r="173">
-      <x:c r="A173" s="10"/>
-      <x:c r="B173" s="10"/>
+      <x:c r="A173" s="11"/>
+      <x:c r="B173" s="11"/>
     </x:row>
     <x:row r="174">
-      <x:c r="A174" s="10"/>
-      <x:c r="B174" s="10"/>
+      <x:c r="A174" s="11"/>
+      <x:c r="B174" s="11"/>
     </x:row>
     <x:row r="175">
-      <x:c r="A175" s="10"/>
-      <x:c r="B175" s="10"/>
+      <x:c r="A175" s="11"/>
+      <x:c r="B175" s="11"/>
     </x:row>
     <x:row r="176">
-      <x:c r="A176" s="10"/>
-      <x:c r="B176" s="10"/>
+      <x:c r="A176" s="11"/>
+      <x:c r="B176" s="11"/>
     </x:row>
     <x:row r="177">
-      <x:c r="A177" s="10"/>
-      <x:c r="B177" s="10"/>
+      <x:c r="A177" s="11"/>
+      <x:c r="B177" s="11"/>
     </x:row>
     <x:row r="178">
-      <x:c r="A178" s="10"/>
-      <x:c r="B178" s="10"/>
+      <x:c r="A178" s="11"/>
+      <x:c r="B178" s="11"/>
     </x:row>
     <x:row r="179">
-      <x:c r="A179" s="10"/>
-      <x:c r="B179" s="10"/>
+      <x:c r="A179" s="11"/>
+      <x:c r="B179" s="11"/>
     </x:row>
     <x:row r="180">
-      <x:c r="A180" s="10"/>
-      <x:c r="B180" s="10"/>
+      <x:c r="A180" s="11"/>
+      <x:c r="B180" s="11"/>
     </x:row>
     <x:row r="181">
-      <x:c r="A181" s="10"/>
-      <x:c r="B181" s="10"/>
+      <x:c r="A181" s="11"/>
+      <x:c r="B181" s="11"/>
     </x:row>
     <x:row r="182">
-      <x:c r="A182" s="10"/>
-      <x:c r="B182" s="10"/>
+      <x:c r="A182" s="11"/>
+      <x:c r="B182" s="11"/>
     </x:row>
     <x:row r="183">
-      <x:c r="A183" s="10"/>
-      <x:c r="B183" s="10"/>
+      <x:c r="A183" s="11"/>
+      <x:c r="B183" s="11"/>
     </x:row>
     <x:row r="184">
-      <x:c r="A184" s="10"/>
-      <x:c r="B184" s="10"/>
+      <x:c r="A184" s="11"/>
+      <x:c r="B184" s="11"/>
     </x:row>
     <x:row r="185">
-      <x:c r="A185" s="10"/>
-      <x:c r="B185" s="10"/>
+      <x:c r="A185" s="11"/>
+      <x:c r="B185" s="11"/>
     </x:row>
     <x:row r="186">
-      <x:c r="A186" s="10"/>
-      <x:c r="B186" s="10"/>
+      <x:c r="A186" s="11"/>
+      <x:c r="B186" s="11"/>
     </x:row>
     <x:row r="187">
-      <x:c r="A187" s="10"/>
-      <x:c r="B187" s="10"/>
+      <x:c r="A187" s="11"/>
+      <x:c r="B187" s="11"/>
     </x:row>
     <x:row r="188">
-      <x:c r="A188" s="10"/>
-      <x:c r="B188" s="10"/>
+      <x:c r="A188" s="11"/>
+      <x:c r="B188" s="11"/>
     </x:row>
     <x:row r="189">
-      <x:c r="A189" s="10"/>
-      <x:c r="B189" s="10"/>
+      <x:c r="A189" s="11"/>
+      <x:c r="B189" s="11"/>
     </x:row>
     <x:row r="190">
-      <x:c r="A190" s="10"/>
-      <x:c r="B190" s="10"/>
+      <x:c r="A190" s="11"/>
+      <x:c r="B190" s="11"/>
     </x:row>
     <x:row r="191">
-      <x:c r="A191" s="10"/>
-      <x:c r="B191" s="10"/>
+      <x:c r="A191" s="11"/>
+      <x:c r="B191" s="11"/>
     </x:row>
     <x:row r="192">
-      <x:c r="A192" s="10"/>
-      <x:c r="B192" s="10"/>
+      <x:c r="A192" s="11"/>
+      <x:c r="B192" s="11"/>
     </x:row>
     <x:row r="193">
-      <x:c r="A193" s="10"/>
-      <x:c r="B193" s="10"/>
+      <x:c r="A193" s="11"/>
+      <x:c r="B193" s="11"/>
     </x:row>
     <x:row r="194">
-      <x:c r="A194" s="10"/>
-      <x:c r="B194" s="10"/>
+      <x:c r="A194" s="11"/>
+      <x:c r="B194" s="11"/>
     </x:row>
     <x:row r="195">
-      <x:c r="A195" s="10"/>
-      <x:c r="B195" s="10"/>
+      <x:c r="A195" s="11"/>
+      <x:c r="B195" s="11"/>
     </x:row>
     <x:row r="196">
-      <x:c r="A196" s="10"/>
-      <x:c r="B196" s="10"/>
+      <x:c r="A196" s="11"/>
+      <x:c r="B196" s="11"/>
     </x:row>
     <x:row r="197">
-      <x:c r="A197" s="10"/>
-      <x:c r="B197" s="10"/>
+      <x:c r="A197" s="11"/>
+      <x:c r="B197" s="11"/>
     </x:row>
     <x:row r="198">
-      <x:c r="A198" s="10"/>
-      <x:c r="B198" s="10"/>
+      <x:c r="A198" s="11"/>
+      <x:c r="B198" s="11"/>
     </x:row>
     <x:row r="199">
-      <x:c r="A199" s="10"/>
-      <x:c r="B199" s="10"/>
+      <x:c r="A199" s="11"/>
+      <x:c r="B199" s="11"/>
     </x:row>
     <x:row r="200">
-      <x:c r="A200" s="10"/>
-      <x:c r="B200" s="10"/>
+      <x:c r="A200" s="11"/>
+      <x:c r="B200" s="11"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
